--- a/public/data/mapeamento.xlsx
+++ b/public/data/mapeamento.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ML_Analytics\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7ADFEC7-D110-4E96-B3B1-77D7905162C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{183388CB-9E7F-4C78-9351-8DCDC53EE19F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{FC2B6D7F-C9EF-49D9-8A04-EEAFC0D58170}"/>
+    <workbookView xWindow="-21720" yWindow="660" windowWidth="21840" windowHeight="13020" xr2:uid="{FC2B6D7F-C9EF-49D9-8A04-EEAFC0D58170}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="82">
   <si>
     <t>SKU</t>
   </si>
@@ -259,6 +259,30 @@
   </si>
   <si>
     <t>UTD-024-BR</t>
+  </si>
+  <si>
+    <t>UTD-040</t>
+  </si>
+  <si>
+    <t>Tábua Frios Redonda Giratória</t>
+  </si>
+  <si>
+    <t>UTD-038</t>
+  </si>
+  <si>
+    <t>Organizador Gaveta extensivel madeira</t>
+  </si>
+  <si>
+    <t>UTD-034</t>
+  </si>
+  <si>
+    <t>Organizador duplo giratorio Multiuso</t>
+  </si>
+  <si>
+    <t>UTD-036</t>
+  </si>
+  <si>
+    <t>Organizador Giratório Bambu fruteira</t>
   </si>
 </sst>
 </file>
@@ -692,13 +716,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DEEB9549-06C1-4187-8BE9-9858633647F1}">
-  <dimension ref="A1:Z69"/>
+  <dimension ref="A1:Z79"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="17.44140625" style="3" customWidth="1"/>
-    <col min="2" max="2" width="17.33203125" style="3" customWidth="1"/>
-    <col min="3" max="3" width="37.5546875" style="3" customWidth="1"/>
-    <col min="4" max="4" width="24" style="6" customWidth="1"/>
+    <col min="1" max="1" width="12.6640625" style="3" customWidth="1"/>
+    <col min="2" max="2" width="14.5546875" style="3" customWidth="1"/>
+    <col min="3" max="3" width="32.33203125" style="3" customWidth="1"/>
+    <col min="4" max="4" width="20.109375" style="6" customWidth="1"/>
     <col min="5" max="26" width="8.88671875" style="3"/>
   </cols>
   <sheetData>
@@ -1088,7 +1112,9 @@
       <c r="C12" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D12" s="4"/>
+      <c r="D12" s="4">
+        <v>64.900000000000006</v>
+      </c>
       <c r="E12" s="1"/>
       <c r="F12" s="1"/>
       <c r="G12" s="1"/>
@@ -1121,7 +1147,7 @@
         <v>18</v>
       </c>
       <c r="D13" s="5">
-        <v>78.900000000000006</v>
+        <v>67.900000000000006</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" s="2"/>
@@ -1154,7 +1180,9 @@
       <c r="C14" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D14" s="4"/>
+      <c r="D14" s="4">
+        <v>67.900000000000006</v>
+      </c>
       <c r="E14" s="1"/>
       <c r="F14" s="1"/>
       <c r="G14" s="1"/>
@@ -1448,7 +1476,7 @@
       <c r="W22" s="1"/>
       <c r="X22" s="1"/>
     </row>
-    <row r="23" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:24" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="2" t="s">
         <v>27</v>
       </c>
@@ -1458,7 +1486,9 @@
       <c r="C23" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="D23" s="5"/>
+      <c r="D23" s="5">
+        <v>78.900000000000006</v>
+      </c>
       <c r="E23" s="2"/>
       <c r="F23" s="2"/>
       <c r="G23" s="2"/>
@@ -1524,7 +1554,9 @@
       <c r="C25" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="D25" s="5"/>
+      <c r="D25" s="5">
+        <v>78.900000000000006</v>
+      </c>
       <c r="E25" s="2"/>
       <c r="F25" s="2"/>
       <c r="G25" s="2"/>
@@ -1557,7 +1589,7 @@
         <v>32</v>
       </c>
       <c r="D26" s="4">
-        <v>69.900000000000006</v>
+        <v>54.9</v>
       </c>
       <c r="E26" s="1"/>
       <c r="F26" s="1"/>
@@ -1590,7 +1622,9 @@
       <c r="C27" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="D27" s="5"/>
+      <c r="D27" s="5">
+        <v>54.9</v>
+      </c>
       <c r="E27" s="2"/>
       <c r="F27" s="2"/>
       <c r="G27" s="2"/>
@@ -1656,7 +1690,9 @@
       <c r="C29" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="D29" s="5"/>
+      <c r="D29" s="5">
+        <v>24.9</v>
+      </c>
       <c r="E29" s="2"/>
       <c r="F29" s="2"/>
       <c r="G29" s="2"/>
@@ -1790,7 +1826,9 @@
       <c r="C33" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="D33" s="5"/>
+      <c r="D33" s="5">
+        <v>78.900000000000006</v>
+      </c>
       <c r="E33" s="2"/>
       <c r="F33" s="2"/>
       <c r="G33" s="2"/>
@@ -3036,6 +3074,314 @@
       <c r="W69" s="2"/>
       <c r="X69" s="2"/>
     </row>
+    <row r="70" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A70" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B70" s="2">
+        <v>4786400917</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="D70" s="5">
+        <v>69.989999999999995</v>
+      </c>
+      <c r="E70" s="2"/>
+      <c r="F70" s="2"/>
+      <c r="G70" s="2"/>
+      <c r="H70" s="2"/>
+      <c r="I70" s="2"/>
+      <c r="J70" s="2"/>
+      <c r="K70" s="2"/>
+      <c r="L70" s="2"/>
+      <c r="M70" s="2"/>
+      <c r="N70" s="2"/>
+      <c r="O70" s="2"/>
+      <c r="P70" s="2"/>
+      <c r="Q70" s="2"/>
+      <c r="R70" s="2"/>
+      <c r="S70" s="2"/>
+      <c r="T70" s="2"/>
+      <c r="U70" s="2"/>
+      <c r="V70" s="2"/>
+      <c r="W70" s="2"/>
+      <c r="X70" s="2"/>
+    </row>
+    <row r="71" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A71" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B71" s="2">
+        <v>4803216111</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="D71" s="5">
+        <v>69.989999999999995</v>
+      </c>
+      <c r="E71" s="2"/>
+      <c r="F71" s="2"/>
+      <c r="G71" s="2"/>
+      <c r="H71" s="2"/>
+      <c r="I71" s="2"/>
+      <c r="J71" s="2"/>
+      <c r="K71" s="2"/>
+      <c r="L71" s="2"/>
+      <c r="M71" s="2"/>
+      <c r="N71" s="2"/>
+      <c r="O71" s="2"/>
+      <c r="P71" s="2"/>
+      <c r="Q71" s="2"/>
+      <c r="R71" s="2"/>
+      <c r="S71" s="2"/>
+      <c r="T71" s="2"/>
+      <c r="U71" s="2"/>
+      <c r="V71" s="2"/>
+      <c r="W71" s="2"/>
+      <c r="X71" s="2"/>
+    </row>
+    <row r="72" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A72" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="B72" s="2">
+        <v>6993953494</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D72" s="5">
+        <v>78.900000000000006</v>
+      </c>
+      <c r="E72" s="2"/>
+      <c r="F72" s="2"/>
+      <c r="G72" s="2"/>
+      <c r="H72" s="2"/>
+      <c r="I72" s="2"/>
+      <c r="J72" s="2"/>
+      <c r="K72" s="2"/>
+      <c r="L72" s="2"/>
+      <c r="M72" s="2"/>
+      <c r="N72" s="2"/>
+      <c r="O72" s="2"/>
+      <c r="P72" s="2"/>
+      <c r="Q72" s="2"/>
+      <c r="R72" s="2"/>
+      <c r="S72" s="2"/>
+      <c r="T72" s="2"/>
+      <c r="U72" s="2"/>
+      <c r="V72" s="2"/>
+      <c r="W72" s="2"/>
+      <c r="X72" s="2"/>
+    </row>
+    <row r="73" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A73" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="B73" s="2">
+        <v>4786362859</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D73" s="5">
+        <v>78.900000000000006</v>
+      </c>
+      <c r="E73" s="2"/>
+      <c r="F73" s="2"/>
+      <c r="G73" s="2"/>
+      <c r="H73" s="2"/>
+      <c r="I73" s="2"/>
+      <c r="J73" s="2"/>
+      <c r="K73" s="2"/>
+      <c r="L73" s="2"/>
+      <c r="M73" s="2"/>
+      <c r="N73" s="2"/>
+      <c r="O73" s="2"/>
+      <c r="P73" s="2"/>
+      <c r="Q73" s="2"/>
+      <c r="R73" s="2"/>
+      <c r="S73" s="2"/>
+      <c r="T73" s="2"/>
+      <c r="U73" s="2"/>
+      <c r="V73" s="2"/>
+      <c r="W73" s="2"/>
+      <c r="X73" s="2"/>
+    </row>
+    <row r="74" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A74" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="B74" s="2">
+        <v>6978059012</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="D74" s="5">
+        <v>78.900000000000006</v>
+      </c>
+      <c r="E74" s="2"/>
+      <c r="F74" s="2"/>
+      <c r="G74" s="2"/>
+      <c r="H74" s="2"/>
+      <c r="I74" s="2"/>
+      <c r="J74" s="2"/>
+      <c r="K74" s="2"/>
+      <c r="L74" s="2"/>
+      <c r="M74" s="2"/>
+      <c r="N74" s="2"/>
+      <c r="O74" s="2"/>
+      <c r="P74" s="2"/>
+      <c r="Q74" s="2"/>
+      <c r="R74" s="2"/>
+      <c r="S74" s="2"/>
+      <c r="T74" s="2"/>
+      <c r="U74" s="2"/>
+      <c r="V74" s="2"/>
+      <c r="W74" s="2"/>
+      <c r="X74" s="2"/>
+    </row>
+    <row r="75" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A75" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B75" s="2">
+        <v>7006602056</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D75" s="5">
+        <v>78.900000000000006</v>
+      </c>
+      <c r="E75" s="2"/>
+      <c r="F75" s="2"/>
+      <c r="G75" s="2"/>
+      <c r="H75" s="2"/>
+      <c r="I75" s="2"/>
+      <c r="J75" s="2"/>
+      <c r="K75" s="2"/>
+      <c r="L75" s="2"/>
+      <c r="M75" s="2"/>
+      <c r="N75" s="2"/>
+      <c r="O75" s="2"/>
+      <c r="P75" s="2"/>
+      <c r="Q75" s="2"/>
+      <c r="R75" s="2"/>
+      <c r="S75" s="2"/>
+      <c r="T75" s="2"/>
+      <c r="U75" s="2"/>
+      <c r="V75" s="2"/>
+      <c r="W75" s="2"/>
+      <c r="X75" s="2"/>
+    </row>
+    <row r="76" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A76" s="2"/>
+      <c r="B76" s="2"/>
+      <c r="C76" s="2"/>
+      <c r="D76" s="5"/>
+      <c r="E76" s="2"/>
+      <c r="F76" s="2"/>
+      <c r="G76" s="2"/>
+      <c r="H76" s="2"/>
+      <c r="I76" s="2"/>
+      <c r="J76" s="2"/>
+      <c r="K76" s="2"/>
+      <c r="L76" s="2"/>
+      <c r="M76" s="2"/>
+      <c r="N76" s="2"/>
+      <c r="O76" s="2"/>
+      <c r="P76" s="2"/>
+      <c r="Q76" s="2"/>
+      <c r="R76" s="2"/>
+      <c r="S76" s="2"/>
+      <c r="T76" s="2"/>
+      <c r="U76" s="2"/>
+      <c r="V76" s="2"/>
+      <c r="W76" s="2"/>
+      <c r="X76" s="2"/>
+    </row>
+    <row r="77" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A77" s="2"/>
+      <c r="B77" s="2"/>
+      <c r="C77" s="2"/>
+      <c r="D77" s="5"/>
+      <c r="E77" s="2"/>
+      <c r="F77" s="2"/>
+      <c r="G77" s="2"/>
+      <c r="H77" s="2"/>
+      <c r="I77" s="2"/>
+      <c r="J77" s="2"/>
+      <c r="K77" s="2"/>
+      <c r="L77" s="2"/>
+      <c r="M77" s="2"/>
+      <c r="N77" s="2"/>
+      <c r="O77" s="2"/>
+      <c r="P77" s="2"/>
+      <c r="Q77" s="2"/>
+      <c r="R77" s="2"/>
+      <c r="S77" s="2"/>
+      <c r="T77" s="2"/>
+      <c r="U77" s="2"/>
+      <c r="V77" s="2"/>
+      <c r="W77" s="2"/>
+      <c r="X77" s="2"/>
+    </row>
+    <row r="78" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A78" s="2"/>
+      <c r="B78" s="2"/>
+      <c r="C78" s="2"/>
+      <c r="D78" s="5"/>
+      <c r="E78" s="2"/>
+      <c r="F78" s="2"/>
+      <c r="G78" s="2"/>
+      <c r="H78" s="2"/>
+      <c r="I78" s="2"/>
+      <c r="J78" s="2"/>
+      <c r="K78" s="2"/>
+      <c r="L78" s="2"/>
+      <c r="M78" s="2"/>
+      <c r="N78" s="2"/>
+      <c r="O78" s="2"/>
+      <c r="P78" s="2"/>
+      <c r="Q78" s="2"/>
+      <c r="R78" s="2"/>
+      <c r="S78" s="2"/>
+      <c r="T78" s="2"/>
+      <c r="U78" s="2"/>
+      <c r="V78" s="2"/>
+      <c r="W78" s="2"/>
+      <c r="X78" s="2"/>
+    </row>
+    <row r="79" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A79" s="2"/>
+      <c r="B79" s="2"/>
+      <c r="C79" s="2"/>
+      <c r="D79" s="5"/>
+      <c r="E79" s="2"/>
+      <c r="F79" s="2"/>
+      <c r="G79" s="2"/>
+      <c r="H79" s="2"/>
+      <c r="I79" s="2"/>
+      <c r="J79" s="2"/>
+      <c r="K79" s="2"/>
+      <c r="L79" s="2"/>
+      <c r="M79" s="2"/>
+      <c r="N79" s="2"/>
+      <c r="O79" s="2"/>
+      <c r="P79" s="2"/>
+      <c r="Q79" s="2"/>
+      <c r="R79" s="2"/>
+      <c r="S79" s="2"/>
+      <c r="T79" s="2"/>
+      <c r="U79" s="2"/>
+      <c r="V79" s="2"/>
+      <c r="W79" s="2"/>
+      <c r="X79" s="2"/>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
